--- a/basedatos_partidas/salida/descompuestos/CT-06-03-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-03-040.xlsx
@@ -539,10 +539,10 @@
         <v>0.85</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>1.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.46</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>1.05</v>
       </c>
       <c r="G12" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.41</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="13">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="G15" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="16">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="18">
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>18.43</v>
+        <v>19.96</v>
       </c>
       <c r="H27" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>18.61</v>
+        <v>20.16</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-03-040.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-03-040.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 06 Paredes y tabiquería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Tabiquería de yeso laminado</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
